--- a/handover/NIKE_Dashboard_FY2020-2026.xlsx
+++ b/handover/NIKE_Dashboard_FY2020-2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\HuyenTrang\doi-moi-sang-tao\nike-financial-dashboard\handover\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BEBB288-9798-4AAF-9DB7-0E9C41CAEE14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3826B018-7D01-4B8E-AC91-0465DFB3F7F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3800" yWindow="3800" windowWidth="18660" windowHeight="11710" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1392,7 +1392,7 @@
     <t>Phân phối và kết quả tài chính của NIKE, FY2020–FY2026</t>
   </si>
   <si>
-    <t>Số liệu từ báo cáo thường niên Form 10-K của NIKE, Inc. nộp Ủy ban Chứng khoán Mỹ (SEC). Năm tài chính kết thúc ngày 31/5.</t>
+    <t>Số liệu lấy từ báo cáo thường niên Form 10-K mà NIKE, Inc. nộp cho Ủy ban Chứng khoán Mỹ (SEC). Năm tài chính của NIKE kết thúc ngày 31/5.</t>
   </si>
   <si>
     <t>Tải bộ dữ liệu Excel</t>
@@ -1404,7 +1404,7 @@
     <t>Mở dashboard web</t>
   </si>
   <si>
-    <t>Bấm một năm để lọc, giữ Ctrl để chọn nhiều năm. Nút xóa lọc ở góc slicer đưa về đủ 7 năm.</t>
+    <t>Bấm một năm để lọc, giữ Ctrl để chọn nhiều năm. Bấm nút xoá lọc ở góc slicer để xem lại đủ 7 năm.</t>
   </si>
   <si>
     <t>Cơ cấu doanh thu giữa NIKE Direct và bán buôn đã thay đổi thế nào trong FY2020–FY2026?</t>
@@ -1416,13 +1416,13 @@
     <t>Cơ cấu doanh thu NIKE Brand theo kênh</t>
   </si>
   <si>
-    <t>Tỷ trọng trong tổng doanh thu NIKE Brand (%), nhóm tự tính từ số liệu 10-K.</t>
+    <t>Tỷ trọng trong tổng doanh thu NIKE Brand (%), do nhóm tự tính từ số liệu 10-K.</t>
   </si>
   <si>
     <t>Doanh thu theo kênh</t>
   </si>
   <si>
-    <t>Tỷ USD, phạm vi NIKE Brand. Số NIKE báo cáo.</t>
+    <t>Tỷ USD, phạm vi NIKE Brand. Số do NIKE công bố.</t>
   </si>
   <si>
     <t>Tăng trưởng so với năm trước</t>
@@ -1463,7 +1463,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">Tỷ trọng kênh dùng mẫu số là doanh thu NIKE Brand. Converse (có kênh trực tiếp riêng) và Corporate nằm ngoài các con số này.
+      <t xml:space="preserve">Tỷ trọng các kênh được tính trên tổng doanh thu NIKE Brand. Converse (có kênh bán trực tiếp riêng) và Corporate không nằm trong các con số này.
 </t>
     </r>
     <r>
@@ -1485,7 +1485,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">NIKE chỉ công bố doanh số Digital trong phần MD&amp;A, làm tròn 0,1 tỷ USD. Số FY2023 được trình bày lại từ 12,6 xuống 12,4 tỷ USD ở 10-K FY2024; khi so FY2024 (12,1 tỷ USD) với năm trước, dùng số 12,4 cùng cách phân loại.
+      <t xml:space="preserve">NIKE chỉ công bố doanh số Digital trong phần MD&amp;A và làm tròn đến 0,1 tỷ USD. Trong 10-K FY2024, số FY2023 được trình bày lại từ 12,6 xuống 12,4 tỷ USD, nên khi so FY2024 (12,1 tỷ USD) với năm trước cần dùng số 12,4 để cùng cách phân loại.
 </t>
     </r>
     <r>
@@ -1507,7 +1507,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">Tăng trưởng theo báo cáo được tính từ doanh thu năm nay và số năm trước trong cùng 10-K. Tăng trưởng loại trừ tỷ giá là chỉ tiêu non-GAAP do NIKE tính, không tự tính lại được.
+      <t xml:space="preserve">Tăng trưởng theo báo cáo được tính từ doanh thu năm nay và số năm trước trong cùng 10-K. Tăng trưởng loại trừ tỷ giá là chỉ tiêu non-GAAP do NIKE tính, nhóm không tự tính lại được.
 </t>
     </r>
     <r>
@@ -1615,7 +1615,7 @@
     <t>Chi phí bán hàng và quản lý</t>
   </si>
   <si>
-    <t>% doanh thu, NIKE, Inc. Hai cấu phần cộng lại bằng tổng SG&amp;A.</t>
+    <t>% doanh thu, NIKE, Inc. Hai phần cộng lại bằng tổng SG&amp;A.</t>
   </si>
   <si>
     <t>Biên EBIT (non-GAAP)</t>
@@ -1654,7 +1654,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>Báo cáo kết quả kinh doanh của NIKE không có dòng tổng phụ này: sau tổng chi phí bán hàng và quản lý là chi phí (thu nhập) lãi thuần và chi phí (thu nhập) khác thuần, rồi đến lợi nhuận trước thuế. EBIT (lợi nhuận sau thuế + chi phí lãi thuần + thuế) là thước đo NIKE tự dùng và ghi rõ là non-GAAP; EBIT vẫn gồm khoản chi phí (thu nhập) khác thuần.</t>
+      <t>Báo cáo kết quả kinh doanh của NIKE không có dòng tổng phụ này: ngay sau tổng chi phí bán hàng và quản lý là chi phí (thu nhập) lãi thuần, chi phí (thu nhập) khác thuần, rồi đến lợi nhuận trước thuế. EBIT (lợi nhuận sau thuế + chi phí lãi thuần + thuế) là chỉ tiêu non-GAAP do NIKE tự định nghĩa, và vẫn bao gồm khoản chi phí (thu nhập) khác thuần.</t>
     </r>
   </si>
   <si>
@@ -1705,7 +1705,7 @@
     <t>Bảng số liệu kết quả tài chính (NIKE, Inc.)</t>
   </si>
   <si>
-    <t>Triệu USD trừ khi ghi khác. Số âm trong ngoặc đơn. Số NIKE công bố có số trang 10-K ở dòng nhỏ ngay dưới (bấm vào số trang để mở báo cáo trên SEC). Số in nghiêng là số nhóm tự tính.</t>
+    <t>Đơn vị triệu USD, trừ khi ghi khác. Số âm để trong ngoặc đơn. Số NIKE công bố có số trang 10-K ở dòng nhỏ ngay dưới (bấm vào số trang để mở báo cáo trên SEC). Số in nghiêng là số nhóm tự tính.</t>
   </si>
   <si>
     <t>Báo cáo kết quả kinh doanh</t>
@@ -1813,19 +1813,19 @@
     <t>Phương pháp</t>
   </si>
   <si>
-    <t>–  Số của năm FY t lấy từ 10-K FY t; số năm trước lấy từ cột so sánh trong cùng báo cáo để tính tăng trưởng, giống cách NIKE tính.</t>
-  </si>
-  <si>
-    <t>–  Số liệu báo cáo đọc từ dữ liệu XBRL gắn trong 10-K, đối chiếu với API XBRL của SEC và với bảng trong phần MD&amp;A.</t>
-  </si>
-  <si>
-    <t>–  Số chỉ có trong phần MD&amp;A (tăng trưởng loại trừ tỷ giá, doanh số Digital) được đọc lại trực tiếp trên trang 10-K bằng một cách thứ hai; ảnh chụp đối chiếu ở trang “Đối chiếu 35 số” của dashboard web.</t>
-  </si>
-  <si>
-    <t>–  Mọi chỉ số tính toán dùng cùng một công thức với sheet 04 của bộ dữ liệu Excel; mỗi lần cập nhật đều chạy kiểm tra đối chiếu số học.</t>
-  </si>
-  <si>
-    <t>–  Số liệu NIKE không công bố được ghi “Không công bố”, không thay bằng 0.</t>
+    <t>–  Số liệu của mỗi năm tài chính được lấy từ báo cáo 10-K của chính năm đó. Khi tính tăng trưởng, số năm trước được lấy ở cột so sánh trong cùng báo cáo, giống cách NIKE tự tính.</t>
+  </si>
+  <si>
+    <t>–  Các số trên báo cáo tài chính được lấy từ dữ liệu XBRL đi kèm mỗi báo cáo 10-K, sau đó đối chiếu với dữ liệu XBRL do SEC công bố và với các bảng trong phần MD&amp;A.</t>
+  </si>
+  <si>
+    <t>–  Các chỉ tiêu chỉ có trong phần MD&amp;A (tăng trưởng loại trừ tỷ giá, doanh số Digital) không có dữ liệu XBRL để đối chiếu, nên được đọc lại thêm một lần ngay trên trang 10-K. Ảnh chụp từng chỗ có ở trang “Đối chiếu 35 số” trên dashboard web.</t>
+  </si>
+  <si>
+    <t>–  Các chỉ số do nhóm tự tính dùng đúng công thức ở sheet 04 của bộ dữ liệu Excel. Mỗi lần cập nhật đều kiểm tra lại các phép cộng trừ, chẳng hạn doanh thu trừ giá vốn phải bằng lợi nhuận gộp.</t>
+  </si>
+  <si>
+    <t>–  Số liệu nào NIKE không công bố thì ghi “Không công bố”, không điền số 0.</t>
   </si>
   <si>
     <t>Tình trạng dữ liệu</t>
@@ -1834,7 +1834,7 @@
     <t>203 số liệu báo cáo: 202 khớp nguồn chính thức, 1 không được NIKE công bố. Dữ liệu trích xuất ngày 23/10/2026.</t>
   </si>
   <si>
-    <t>Sản phẩm học tập của sinh viên, không liên kết với NIKE, Inc.</t>
+    <t>Sản phẩm học tập của sinh viên, không liên quan đến NIKE, Inc.</t>
   </si>
   <si>
     <t>Liên kết</t>
@@ -1981,9 +1981,8 @@
       <family val="2"/>
     </font>
     <font>
-      <u/>
       <sz val="8"/>
-      <color rgb="FF5B6472"/>
+      <color rgb="FF6F7784"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -2407,7 +2406,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-E6F4-4337-9664-2DDF34F8B3DB}"/>
+              <c16:uniqueId val="{00000000-F4B5-421A-997A-836B45E9A47C}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2527,7 +2526,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-E6F4-4337-9664-2DDF34F8B3DB}"/>
+              <c16:uniqueId val="{00000001-F4B5-421A-997A-836B45E9A47C}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2607,7 +2606,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-E6F4-4337-9664-2DDF34F8B3DB}"/>
+              <c16:uniqueId val="{00000002-F4B5-421A-997A-836B45E9A47C}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2903,7 +2902,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-2A3E-4A10-B328-C4A9815C00DE}"/>
+              <c16:uniqueId val="{00000000-684C-447F-AA2D-C23FB3A8C617}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3167,7 +3166,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-8C42-477F-B586-9DE760BCB3CE}"/>
+              <c16:uniqueId val="{00000000-0838-4C6A-8F63-22020B8CD90C}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3284,7 +3283,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-8C42-477F-B586-9DE760BCB3CE}"/>
+              <c16:uniqueId val="{00000001-0838-4C6A-8F63-22020B8CD90C}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3527,7 +3526,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-56B8-410B-AFBD-07ED00241AB9}"/>
+              <c16:uniqueId val="{00000000-EBA7-4880-9044-1C80B83B1A2B}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3607,7 +3606,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-56B8-410B-AFBD-07ED00241AB9}"/>
+              <c16:uniqueId val="{00000001-EBA7-4880-9044-1C80B83B1A2B}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3886,7 +3885,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-AEBE-46E0-BEDA-2849DD251F61}"/>
+              <c16:uniqueId val="{00000000-F417-4F26-A605-000884B78667}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3966,7 +3965,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-AEBE-46E0-BEDA-2849DD251F61}"/>
+              <c16:uniqueId val="{00000001-F417-4F26-A605-000884B78667}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4247,7 +4246,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-DEC5-49C6-B94E-3FCE21F22EA8}"/>
+              <c16:uniqueId val="{00000000-BEBA-43D1-A3F5-4CD015266C1C}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4521,7 +4520,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-A2A8-4799-B71A-8C85B1AB72CB}"/>
+              <c16:uniqueId val="{00000000-D4EC-4C5E-B7BC-951AD9C5D377}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4750,7 +4749,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-E3AE-471E-86E1-72DAB67C6D9A}"/>
+              <c16:uniqueId val="{00000000-0B06-4BD7-B808-7446FB41F79A}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4832,7 +4831,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-E3AE-471E-86E1-72DAB67C6D9A}"/>
+              <c16:uniqueId val="{00000001-0B06-4BD7-B808-7446FB41F79A}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4966,7 +4965,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-E3AE-471E-86E1-72DAB67C6D9A}"/>
+              <c16:uniqueId val="{00000002-0B06-4BD7-B808-7446FB41F79A}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -5264,7 +5263,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-12C0-4339-ABB7-BDC3988B92C5}"/>
+              <c16:uniqueId val="{00000000-2235-45FF-898C-5A0FF4324209}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -5526,7 +5525,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-C6A1-43AF-972F-A31EF44CE3A0}"/>
+              <c16:uniqueId val="{00000000-ABB1-4BDC-8308-E446A604ACBE}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -5819,7 +5818,7 @@
             <xdr:cNvPr id="6" name="sl_tblNam1">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2BAEB838-4191-21D3-A4C9-34D54110C61B}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E4D652F0-2B89-4882-22A6-07FF7C6CFCD0}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -5897,7 +5896,7 @@
             <xdr:cNvPr id="7" name="sl_tblCoSo1">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{62BD186F-8DF3-A27D-E781-116D886AF64C}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3046B924-557A-C8DD-B57C-D05EC064C562}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -6196,7 +6195,7 @@
             <xdr:cNvPr id="8" name="sl_tblNam2">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0DCF57A1-710B-4F52-74CA-25C843332132}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5F74DE0C-BF96-D71B-1C77-5D1CB31AFB1B}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -6258,7 +6257,7 @@
 </file>
 
 <file path=xl/slicerCaches/slicerCache1.xml><?xml version="1.0" encoding="utf-8"?>
-<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_Năm_tài_chính" xr10:uid="{C88168E4-E2EF-4B1D-9740-338FCFC33F57}" sourceName="Năm tài chính">
+<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_Năm_tài_chính" xr10:uid="{9FCC4910-C2E4-4797-9A4D-FAE540B2F395}" sourceName="Năm tài chính">
   <extLst>
     <x:ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{2F2917AC-EB37-4324-AD4E-5DD8C200BD13}">
       <x15:tableSlicerCache tableId="1" column="1"/>
@@ -6268,7 +6267,7 @@
 </file>
 
 <file path=xl/slicerCaches/slicerCache2.xml><?xml version="1.0" encoding="utf-8"?>
-<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_Cơ_sở_tính_tăng_trưởng" xr10:uid="{5BB7A63C-B99E-4182-8D9D-D74DC64C54F2}" sourceName="Cơ sở tính tăng trưởng">
+<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_Cơ_sở_tính_tăng_trưởng" xr10:uid="{801E203E-EBBE-48C2-8934-94D04E7BFD79}" sourceName="Cơ sở tính tăng trưởng">
   <extLst>
     <x:ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{2F2917AC-EB37-4324-AD4E-5DD8C200BD13}">
       <x15:tableSlicerCache tableId="2" column="1" sortOrder="descending"/>
@@ -6279,14 +6278,14 @@
 
 <file path=xl/slicers/slicer1.xml><?xml version="1.0" encoding="utf-8"?>
 <slicers xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10">
-  <slicer name="sl_tblNam1" xr10:uid="{E7A8146B-FA21-4E6E-BB0C-46930A7C8C0D}" cache="Slicer_Năm_tài_chính" caption="Năm tài chính" columnCount="7" rowHeight="220133"/>
-  <slicer name="sl_tblCoSo1" xr10:uid="{12A6CE97-EC2F-4A67-9A86-561EB1190DEB}" cache="Slicer_Cơ_sở_tính_tăng_trưởng" caption="Cơ sở tính tăng trưởng" columnCount="2" rowHeight="220133"/>
+  <slicer name="sl_tblNam1" xr10:uid="{4BE8442A-538E-4739-87F0-504999243F58}" cache="Slicer_Năm_tài_chính" caption="Năm tài chính" columnCount="7" rowHeight="220133"/>
+  <slicer name="sl_tblCoSo1" xr10:uid="{B8682230-0F0F-4EE5-BDAA-2321871BD854}" cache="Slicer_Cơ_sở_tính_tăng_trưởng" caption="Cơ sở tính tăng trưởng" columnCount="2" rowHeight="220133"/>
 </slicers>
 </file>
 
 <file path=xl/slicers/slicer2.xml><?xml version="1.0" encoding="utf-8"?>
 <slicers xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10">
-  <slicer name="sl_tblNam2" xr10:uid="{4BE97AC0-1A0C-4327-82B6-42441E11CCFD}" cache="Slicer_Năm_tài_chính" caption="Năm tài chính" columnCount="7" rowHeight="220133"/>
+  <slicer name="sl_tblNam2" xr10:uid="{89E8F336-86D3-4511-9EE7-96D8152F0705}" cache="Slicer_Năm_tài_chính" caption="Năm tài chính" columnCount="7" rowHeight="220133"/>
 </slicers>
 </file>
 
@@ -6745,7 +6744,7 @@
       <c r="G13" s="33"/>
       <c r="I13" s="35" t="str">
         <f>'Dữ liệu biểu đồ'!$C$27</f>
-        <v>Tỷ trọng NIKE Direct trong doanh thu NIKE Brand là 34,8% ở FY2020 và 39,2% ở FY2026; cao nhất 43,7% (FY2023), thấp nhất 34,8% (FY2020). Doanh thu NIKE Direct từ 12,4 đến 17,7 tỷ USD; bán buôn từ 23,2 đến 27,5 tỷ USD.</v>
+        <v>Tỷ trọng NIKE Direct trong doanh thu NIKE Brand là 34,8% ở FY2020 và 39,2% ở FY2026, cao nhất 43,7% (FY2023). Doanh thu NIKE Direct đi từ 12,4 đến 17,7 tỷ USD, còn bán buôn từ 23,2 đến 27,5 tỷ USD.</v>
       </c>
       <c r="J13" s="35"/>
       <c r="K13" s="35"/>
@@ -6883,7 +6882,7 @@
       <c r="G41" s="37"/>
       <c r="H41" s="37" t="str">
         <f>'Dữ liệu biểu đồ'!$C$29</f>
-        <v>Thay đổi so với năm trước (%), theo báo cáo, phạm vi NIKE Brand; nhóm tự tính từ 10-K.</v>
+        <v>Thay đổi so với năm trước (%), theo báo cáo, phạm vi NIKE Brand. Nhóm tự tính từ 10-K.</v>
       </c>
       <c r="I41" s="37"/>
       <c r="J41" s="37"/>
@@ -7070,8 +7069,8 @@
     </row>
     <row r="78" spans="2:13" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B78" s="38" t="str">
-        <f>"Nguồn: MD&amp;A (Item 7), đoạn về NIKE Direct; NIKE Direct từ thuyết minh “Revenues”."&amp;'Dữ liệu biểu đồ'!$C$31</f>
-        <v>Nguồn: MD&amp;A (Item 7), đoạn về NIKE Direct; NIKE Direct từ thuyết minh “Revenues”. Báo cáo: 10-K FY2020–FY2026 (danh sách ở sheet “Nguồn và phương pháp”).</v>
+        <f>"Nguồn: MD&amp;A (Item 7), đoạn nói về NIKE Direct. Số NIKE Direct lấy từ thuyết minh “Revenues”."&amp;'Dữ liệu biểu đồ'!$C$31</f>
+        <v>Nguồn: MD&amp;A (Item 7), đoạn nói về NIKE Direct. Số NIKE Direct lấy từ thuyết minh “Revenues”. Báo cáo: 10-K FY2020–FY2026 (danh sách ở sheet “Nguồn và phương pháp”).</v>
       </c>
       <c r="C78" s="38"/>
       <c r="D78" s="38"/>
@@ -8243,7 +8242,7 @@
       <c r="G13" s="33"/>
       <c r="I13" s="35" t="str">
         <f>'Dữ liệu biểu đồ'!$C$28</f>
-        <v>Doanh thu NIKE, Inc. từ 37,4 (FY2020) đến 46,4 tỷ USD (FY2026). Biên lợi nhuận gộp 43,4% (FY2020) và 42,9% (FY2026); biên EBIT (non-GAAP) 8,0% (FY2020) và 8,3% (FY2026), cao nhất 15,5% (FY2021). Hàng tồn kho cuối kỳ từ 7,4 đến 7,5 tỷ USD.</v>
+        <v>Doanh thu NIKE, Inc. đi từ 37,4 (FY2020) đến 46,4 tỷ USD (FY2026). Biên lợi nhuận gộp là 43,4% (FY2020) và 42,9% (FY2026), còn biên EBIT (non-GAAP) là 8,0% (FY2020) và 8,3% (FY2026), cao nhất 15,5% (FY2021). Hàng tồn kho cuối kỳ đi từ 7,4 đến 7,5 tỷ USD.</v>
       </c>
       <c r="J13" s="35"/>
       <c r="K13" s="35"/>
@@ -8352,15 +8351,15 @@
       <c r="D34" s="38"/>
       <c r="E34" s="38"/>
       <c r="F34" s="38" t="str">
-        <f>"Nguồn: Consolidated Statements of Income; biên gộp do nhóm tự tính."&amp;'Dữ liệu biểu đồ'!$C$31</f>
-        <v>Nguồn: Consolidated Statements of Income; biên gộp do nhóm tự tính. Báo cáo: 10-K FY2020–FY2026 (danh sách ở sheet “Nguồn và phương pháp”).</v>
+        <f>"Nguồn: Consolidated Statements of Income. Biên lợi nhuận gộp do nhóm tự tính."&amp;'Dữ liệu biểu đồ'!$C$31</f>
+        <v>Nguồn: Consolidated Statements of Income. Biên lợi nhuận gộp do nhóm tự tính. Báo cáo: 10-K FY2020–FY2026 (danh sách ở sheet “Nguồn và phương pháp”).</v>
       </c>
       <c r="G34" s="38"/>
       <c r="H34" s="38"/>
       <c r="I34" s="38"/>
       <c r="J34" s="38" t="str">
-        <f>"Nguồn: Consolidated Statements of Income; tỷ lệ do nhóm tự tính. Nhãn trên cột là tổng SG&amp;A / doanh thu."&amp;'Dữ liệu biểu đồ'!$C$31</f>
-        <v>Nguồn: Consolidated Statements of Income; tỷ lệ do nhóm tự tính. Nhãn trên cột là tổng SG&amp;A / doanh thu. Báo cáo: 10-K FY2020–FY2026 (danh sách ở sheet “Nguồn và phương pháp”).</v>
+        <f>"Nguồn: Consolidated Statements of Income. Tỷ lệ do nhóm tự tính. Nhãn trên cột là tổng SG&amp;A / doanh thu."&amp;'Dữ liệu biểu đồ'!$C$31</f>
+        <v>Nguồn: Consolidated Statements of Income. Tỷ lệ do nhóm tự tính. Nhãn trên cột là tổng SG&amp;A / doanh thu. Báo cáo: 10-K FY2020–FY2026 (danh sách ở sheet “Nguồn và phương pháp”).</v>
       </c>
       <c r="K34" s="38"/>
       <c r="L34" s="38"/>
@@ -8408,8 +8407,8 @@
     </row>
     <row r="51" spans="2:13" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="38" t="str">
-        <f>"Nguồn: bảng EBIT trong MD&amp;A (Item 7) và Consolidated Statements of Income; biên EBIT do nhóm tự tính."&amp;'Dữ liệu biểu đồ'!$C$31</f>
-        <v>Nguồn: bảng EBIT trong MD&amp;A (Item 7) và Consolidated Statements of Income; biên EBIT do nhóm tự tính. Báo cáo: 10-K FY2020–FY2026 (danh sách ở sheet “Nguồn và phương pháp”).</v>
+        <f>"Nguồn: bảng EBIT trong MD&amp;A (Item 7) và Consolidated Statements of Income. Biên EBIT do nhóm tự tính."&amp;'Dữ liệu biểu đồ'!$C$31</f>
+        <v>Nguồn: bảng EBIT trong MD&amp;A (Item 7) và Consolidated Statements of Income. Biên EBIT do nhóm tự tính. Báo cáo: 10-K FY2020–FY2026 (danh sách ở sheet “Nguồn và phương pháp”).</v>
       </c>
       <c r="C51" s="38"/>
       <c r="D51" s="38"/>
@@ -8422,8 +8421,8 @@
       <c r="H51" s="38"/>
       <c r="I51" s="38"/>
       <c r="J51" s="38" t="str">
-        <f>"Nguồn: Consolidated Balance Sheets và Statements of Income; chỉ số do nhóm tự tính."&amp;'Dữ liệu biểu đồ'!$C$31</f>
-        <v>Nguồn: Consolidated Balance Sheets và Statements of Income; chỉ số do nhóm tự tính. Báo cáo: 10-K FY2020–FY2026 (danh sách ở sheet “Nguồn và phương pháp”).</v>
+        <f>"Nguồn: Consolidated Balance Sheets và Statements of Income. Chỉ số do nhóm tự tính."&amp;'Dữ liệu biểu đồ'!$C$31</f>
+        <v>Nguồn: Consolidated Balance Sheets và Statements of Income. Chỉ số do nhóm tự tính. Báo cáo: 10-K FY2020–FY2026 (danh sách ở sheet “Nguồn và phương pháp”).</v>
       </c>
       <c r="K51" s="38"/>
       <c r="L51" s="38"/>
@@ -10197,7 +10196,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="5" spans="2:4" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:4" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="21" t="s">
         <v>528</v>
       </c>
@@ -10205,7 +10204,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="6" spans="2:4" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:4" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="21" t="s">
         <v>529</v>
       </c>
@@ -10213,7 +10212,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="7" spans="2:4" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:4" ht="63" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="21" t="s">
         <v>530</v>
       </c>
@@ -10221,7 +10220,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="8" spans="2:4" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:4" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="21" t="s">
         <v>531</v>
       </c>
@@ -10229,7 +10228,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="9" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:4" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="21" t="s">
         <v>532</v>
       </c>
@@ -11156,8 +11155,8 @@
         <v>103</v>
       </c>
       <c r="C27" t="str">
-        <f>IF($C$21=$C$22,"Trong FY"&amp;$C$21&amp;", NIKE Direct chiếm "&amp;INDEX($W$5:$W$11,$C$21-2019)&amp;" doanh thu NIKE Brand ("&amp;INDEX($Y$5:$Y$11,$C$21-2019)&amp;" tỷ USD); bán buôn chiếm "&amp;INDEX($X$5:$X$11,$C$21-2019)&amp;" ("&amp;INDEX($Z$5:$Z$11,$C$21-2019)&amp;" tỷ USD).","Tỷ trọng NIKE Direct trong doanh thu NIKE Brand là "&amp;INDEX($W$5:$W$11,$C$21-2019)&amp;" ở FY"&amp;$C$21&amp;" và "&amp;INDEX($W$5:$W$11,$C$22-2019)&amp;" ở FY"&amp;$C$22&amp;IF($C$23&gt;2,"; cao nhất "&amp;INDEX($W$5:$W$11,$C$24-2019)&amp;" (FY"&amp;$C$24&amp;"), thấp nhất "&amp;INDEX($W$5:$W$11,$C$25-2019)&amp;" (FY"&amp;$C$25&amp;")","")&amp;". Doanh thu NIKE Direct từ "&amp;INDEX($Y$5:$Y$11,$C$21-2019)&amp;" đến "&amp;INDEX($Y$5:$Y$11,$C$22-2019)&amp;" tỷ USD; bán buôn từ "&amp;INDEX($Z$5:$Z$11,$C$21-2019)&amp;" đến "&amp;INDEX($Z$5:$Z$11,$C$22-2019)&amp;" tỷ USD.")</f>
-        <v>Tỷ trọng NIKE Direct trong doanh thu NIKE Brand là 34,8% ở FY2020 và 39,2% ở FY2026; cao nhất 43,7% (FY2023), thấp nhất 34,8% (FY2020). Doanh thu NIKE Direct từ 12,4 đến 17,7 tỷ USD; bán buôn từ 23,2 đến 27,5 tỷ USD.</v>
+        <f>IF($C$21=$C$22,"Trong FY"&amp;$C$21&amp;", NIKE Direct chiếm "&amp;INDEX($W$5:$W$11,$C$21-2019)&amp;" doanh thu NIKE Brand ("&amp;INDEX($Y$5:$Y$11,$C$21-2019)&amp;" tỷ USD), còn bán buôn chiếm "&amp;INDEX($X$5:$X$11,$C$21-2019)&amp;" ("&amp;INDEX($Z$5:$Z$11,$C$21-2019)&amp;" tỷ USD).","Tỷ trọng NIKE Direct trong doanh thu NIKE Brand là "&amp;INDEX($W$5:$W$11,$C$21-2019)&amp;" ở FY"&amp;$C$21&amp;" và "&amp;INDEX($W$5:$W$11,$C$22-2019)&amp;" ở FY"&amp;$C$22&amp;IF(AND($C$24&lt;&gt;$C$21,$C$24&lt;&gt;$C$22),", cao nhất "&amp;INDEX($W$5:$W$11,$C$24-2019)&amp;" (FY"&amp;$C$24&amp;")","")&amp;IF(AND($C$25&lt;&gt;$C$21,$C$25&lt;&gt;$C$22),IF(AND($C$24&lt;&gt;$C$21,$C$24&lt;&gt;$C$22)," và thấp nhất ",", thấp nhất ")&amp;INDEX($W$5:$W$11,$C$25-2019)&amp;" (FY"&amp;$C$25&amp;")","")&amp;". Doanh thu NIKE Direct đi từ "&amp;INDEX($Y$5:$Y$11,$C$21-2019)&amp;" đến "&amp;INDEX($Y$5:$Y$11,$C$22-2019)&amp;" tỷ USD, còn bán buôn từ "&amp;INDEX($Z$5:$Z$11,$C$21-2019)&amp;" đến "&amp;INDEX($Z$5:$Z$11,$C$22-2019)&amp;" tỷ USD.")</f>
+        <v>Tỷ trọng NIKE Direct trong doanh thu NIKE Brand là 34,8% ở FY2020 và 39,2% ở FY2026, cao nhất 43,7% (FY2023). Doanh thu NIKE Direct đi từ 12,4 đến 17,7 tỷ USD, còn bán buôn từ 23,2 đến 27,5 tỷ USD.</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
@@ -11165,8 +11164,8 @@
         <v>104</v>
       </c>
       <c r="C28" t="str">
-        <f>IF($C$21=$C$22,"Trong FY"&amp;$C$21&amp;", doanh thu NIKE, Inc. là "&amp;INDEX($AA$5:$AA$11,$C$21-2019)&amp;" tỷ USD, biên lợi nhuận gộp "&amp;INDEX($AB$5:$AB$11,$C$21-2019)&amp;", biên EBIT (non-GAAP) "&amp;INDEX($AC$5:$AC$11,$C$21-2019)&amp;", hàng tồn kho cuối kỳ "&amp;INDEX($AD$5:$AD$11,$C$21-2019)&amp;" tỷ USD.","Doanh thu NIKE, Inc. từ "&amp;INDEX($AA$5:$AA$11,$C$21-2019)&amp;" (FY"&amp;$C$21&amp;") đến "&amp;INDEX($AA$5:$AA$11,$C$22-2019)&amp;" tỷ USD (FY"&amp;$C$22&amp;"). Biên lợi nhuận gộp "&amp;INDEX($AB$5:$AB$11,$C$21-2019)&amp;" (FY"&amp;$C$21&amp;") và "&amp;INDEX($AB$5:$AB$11,$C$22-2019)&amp;" (FY"&amp;$C$22&amp;"); biên EBIT (non-GAAP) "&amp;INDEX($AC$5:$AC$11,$C$21-2019)&amp;" (FY"&amp;$C$21&amp;") và "&amp;INDEX($AC$5:$AC$11,$C$22-2019)&amp;" (FY"&amp;$C$22&amp;")"&amp;IF($C$23&gt;2,", cao nhất "&amp;INDEX($AC$5:$AC$11,$C$26-2019)&amp;" (FY"&amp;$C$26&amp;")","")&amp;". Hàng tồn kho cuối kỳ từ "&amp;INDEX($AD$5:$AD$11,$C$21-2019)&amp;" đến "&amp;INDEX($AD$5:$AD$11,$C$22-2019)&amp;" tỷ USD.")</f>
-        <v>Doanh thu NIKE, Inc. từ 37,4 (FY2020) đến 46,4 tỷ USD (FY2026). Biên lợi nhuận gộp 43,4% (FY2020) và 42,9% (FY2026); biên EBIT (non-GAAP) 8,0% (FY2020) và 8,3% (FY2026), cao nhất 15,5% (FY2021). Hàng tồn kho cuối kỳ từ 7,4 đến 7,5 tỷ USD.</v>
+        <f>IF($C$21=$C$22,"Trong FY"&amp;$C$21&amp;", doanh thu NIKE, Inc. là "&amp;INDEX($AA$5:$AA$11,$C$21-2019)&amp;" tỷ USD, biên lợi nhuận gộp "&amp;INDEX($AB$5:$AB$11,$C$21-2019)&amp;", biên EBIT (non-GAAP) "&amp;INDEX($AC$5:$AC$11,$C$21-2019)&amp;", hàng tồn kho cuối kỳ "&amp;INDEX($AD$5:$AD$11,$C$21-2019)&amp;" tỷ USD.","Doanh thu NIKE, Inc. đi từ "&amp;INDEX($AA$5:$AA$11,$C$21-2019)&amp;" (FY"&amp;$C$21&amp;") đến "&amp;INDEX($AA$5:$AA$11,$C$22-2019)&amp;" tỷ USD (FY"&amp;$C$22&amp;"). Biên lợi nhuận gộp là "&amp;INDEX($AB$5:$AB$11,$C$21-2019)&amp;" (FY"&amp;$C$21&amp;") và "&amp;INDEX($AB$5:$AB$11,$C$22-2019)&amp;" (FY"&amp;$C$22&amp;"), còn biên EBIT (non-GAAP) là "&amp;INDEX($AC$5:$AC$11,$C$21-2019)&amp;" (FY"&amp;$C$21&amp;") và "&amp;INDEX($AC$5:$AC$11,$C$22-2019)&amp;" (FY"&amp;$C$22&amp;")"&amp;IF(AND($C$26&lt;&gt;$C$21,$C$26&lt;&gt;$C$22),", cao nhất "&amp;INDEX($AC$5:$AC$11,$C$26-2019)&amp;" (FY"&amp;$C$26&amp;")","")&amp;". Hàng tồn kho cuối kỳ đi từ "&amp;INDEX($AD$5:$AD$11,$C$21-2019)&amp;" đến "&amp;INDEX($AD$5:$AD$11,$C$22-2019)&amp;" tỷ USD.")</f>
+        <v>Doanh thu NIKE, Inc. đi từ 37,4 (FY2020) đến 46,4 tỷ USD (FY2026). Biên lợi nhuận gộp là 43,4% (FY2020) và 42,9% (FY2026), còn biên EBIT (non-GAAP) là 8,0% (FY2020) và 8,3% (FY2026), cao nhất 15,5% (FY2021). Hàng tồn kho cuối kỳ đi từ 7,4 đến 7,5 tỷ USD.</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
@@ -11174,8 +11173,8 @@
         <v>105</v>
       </c>
       <c r="C29" t="str">
-        <f>IF('Dữ liệu biểu đồ'!$C$20="cn","Thay đổi so với năm trước (%), loại trừ tỷ giá, phạm vi NIKE Brand; số NIKE công bố (non-GAAP).","Thay đổi so với năm trước (%), theo báo cáo, phạm vi NIKE Brand; nhóm tự tính từ 10-K.")</f>
-        <v>Thay đổi so với năm trước (%), theo báo cáo, phạm vi NIKE Brand; nhóm tự tính từ 10-K.</v>
+        <f>IF('Dữ liệu biểu đồ'!$C$20="cn","Thay đổi so với năm trước (%), loại trừ tỷ giá, phạm vi NIKE Brand. Số do NIKE công bố (non-GAAP).","Thay đổi so với năm trước (%), theo báo cáo, phạm vi NIKE Brand. Nhóm tự tính từ 10-K.")</f>
+        <v>Thay đổi so với năm trước (%), theo báo cáo, phạm vi NIKE Brand. Nhóm tự tính từ 10-K.</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
@@ -11183,7 +11182,7 @@
         <v>106</v>
       </c>
       <c r="C30" t="str">
-        <f>IF('Dữ liệu biểu đồ'!$C$20="cn","Nguồn: bảng doanh thu trong MD&amp;A (Item 7), cột “% change excluding currency changes”; NIKE làm tròn đến số nguyên.","Nguồn: thuyết minh “Revenues” trong Form 10-K. Tăng trưởng tính từ số năm nay và số năm trước trong cùng 10-K.")</f>
+        <f>IF('Dữ liệu biểu đồ'!$C$20="cn","Nguồn: bảng doanh thu trong MD&amp;A (Item 7), cột “% change excluding currency changes”. NIKE làm tròn đến số nguyên.","Nguồn: thuyết minh “Revenues” trong Form 10-K. Tăng trưởng tính từ số năm nay và số năm trước trong cùng 10-K.")</f>
         <v>Nguồn: thuyết minh “Revenues” trong Form 10-K. Tăng trưởng tính từ số năm nay và số năm trước trong cùng 10-K.</v>
       </c>
     </row>

--- a/handover/NIKE_Dashboard_FY2020-2026.xlsx
+++ b/handover/NIKE_Dashboard_FY2020-2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\HuyenTrang\doi-moi-sang-tao\nike-financial-dashboard\handover\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3826B018-7D01-4B8E-AC91-0465DFB3F7F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8899FF96-FE6C-4D55-B6B5-73081F50DBE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3800" yWindow="3800" windowWidth="18660" windowHeight="11710" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1392,7 +1392,7 @@
     <t>Phân phối và kết quả tài chính của NIKE, FY2020–FY2026</t>
   </si>
   <si>
-    <t>Số liệu lấy từ báo cáo thường niên Form 10-K mà NIKE, Inc. nộp cho Ủy ban Chứng khoán Mỹ (SEC). Năm tài chính của NIKE kết thúc ngày 31/5.</t>
+    <t>Số liệu lấy từ báo cáo thường niên Form 10‑K mà NIKE, Inc. nộp cho Ủy ban Chứng khoán Mỹ (SEC). Năm tài chính của NIKE kết thúc ngày 31/5.</t>
   </si>
   <si>
     <t>Tải bộ dữ liệu Excel</t>
@@ -1404,7 +1404,7 @@
     <t>Mở dashboard web</t>
   </si>
   <si>
-    <t>Bấm một năm để lọc, giữ Ctrl để chọn nhiều năm. Bấm nút xoá lọc ở góc slicer để xem lại đủ 7 năm.</t>
+    <t>Bấm một năm để lọc, giữ Ctrl để chọn nhiều năm. Bấm nút xóa lọc ở góc slicer để xem lại đủ 7 năm.</t>
   </si>
   <si>
     <t>Cơ cấu doanh thu giữa NIKE Direct và bán buôn đã thay đổi thế nào trong FY2020–FY2026?</t>
@@ -1416,7 +1416,7 @@
     <t>Cơ cấu doanh thu NIKE Brand theo kênh</t>
   </si>
   <si>
-    <t>Tỷ trọng trong tổng doanh thu NIKE Brand (%), do nhóm tự tính từ số liệu 10-K.</t>
+    <t>Tỷ trọng trong tổng doanh thu NIKE Brand (%), do nhóm tự tính từ số liệu 10‑K.</t>
   </si>
   <si>
     <t>Doanh thu theo kênh</t>
@@ -1485,7 +1485,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">NIKE chỉ công bố doanh số Digital trong phần MD&amp;A và làm tròn đến 0,1 tỷ USD. Trong 10-K FY2024, số FY2023 được trình bày lại từ 12,6 xuống 12,4 tỷ USD, nên khi so FY2024 (12,1 tỷ USD) với năm trước cần dùng số 12,4 để cùng cách phân loại.
+      <t xml:space="preserve">NIKE chỉ công bố doanh số Digital trong phần MD&amp;A và làm tròn đến 0,1 tỷ USD. Trong 10‑K FY2024, số FY2023 được trình bày lại từ 12,6 xuống 12,4 tỷ USD, nên khi so FY2024 (12,1 tỷ USD) với năm trước cần dùng số 12,4 để cùng cách phân loại.
 </t>
     </r>
     <r>
@@ -1507,7 +1507,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">Tăng trưởng theo báo cáo được tính từ doanh thu năm nay và số năm trước trong cùng 10-K. Tăng trưởng loại trừ tỷ giá là chỉ tiêu non-GAAP do NIKE tính, nhóm không tự tính lại được.
+      <t xml:space="preserve">Tăng trưởng theo báo cáo được tính từ doanh thu năm nay và số năm trước trong cùng 10‑K. Tăng trưởng loại trừ tỷ giá là chỉ tiêu non‑GAAP do NIKE tính, nhóm không tự tính lại được.
 </t>
     </r>
     <r>
@@ -1537,7 +1537,7 @@
     <t>Bảng số liệu kênh phân phối</t>
   </si>
   <si>
-    <t>Số NIKE công bố có số trang 10-K ở dòng nhỏ ngay dưới (bấm vào số trang để mở báo cáo trên SEC). Số in nghiêng là số nhóm tự tính.</t>
+    <t>Số NIKE công bố có số trang 10‑K ở dòng nhỏ ngay dưới (bấm vào số trang để mở báo cáo trên SEC). Số in nghiêng là số nhóm tự tính.</t>
   </si>
   <si>
     <t>Chỉ tiêu</t>
@@ -1576,13 +1576,13 @@
     <t>NIKE Direct, theo báo cáo</t>
   </si>
   <si>
-    <t>NIKE Direct, loại trừ tỷ giá (non-GAAP)</t>
+    <t>NIKE Direct, loại trừ tỷ giá (non‑GAAP)</t>
   </si>
   <si>
     <t>Bán buôn, theo báo cáo</t>
   </si>
   <si>
-    <t>Bán buôn, loại trừ tỷ giá (non-GAAP)</t>
+    <t>Bán buôn, loại trừ tỷ giá (non‑GAAP)</t>
   </si>
   <si>
     <t>NIKE Brand, theo báo cáo</t>
@@ -1618,7 +1618,7 @@
     <t>% doanh thu, NIKE, Inc. Hai phần cộng lại bằng tổng SG&amp;A.</t>
   </si>
   <si>
-    <t>Biên EBIT (non-GAAP)</t>
+    <t>Biên EBIT (non‑GAAP)</t>
   </si>
   <si>
     <t>% doanh thu, NIKE, Inc.</t>
@@ -1654,7 +1654,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>Báo cáo kết quả kinh doanh của NIKE không có dòng tổng phụ này: ngay sau tổng chi phí bán hàng và quản lý là chi phí (thu nhập) lãi thuần, chi phí (thu nhập) khác thuần, rồi đến lợi nhuận trước thuế. EBIT (lợi nhuận sau thuế + chi phí lãi thuần + thuế) là chỉ tiêu non-GAAP do NIKE tự định nghĩa, và vẫn bao gồm khoản chi phí (thu nhập) khác thuần.</t>
+      <t>Báo cáo kết quả kinh doanh của NIKE không có dòng tổng phụ này: ngay sau tổng chi phí bán hàng và quản lý là chi phí (thu nhập) lãi thuần, chi phí (thu nhập) khác thuần, rồi đến lợi nhuận trước thuế. EBIT (lợi nhuận sau thuế + chi phí lãi thuần + thuế) là chỉ tiêu non‑GAAP do NIKE tự định nghĩa, và vẫn bao gồm khoản chi phí (thu nhập) khác thuần.</t>
     </r>
   </si>
   <si>
@@ -1705,7 +1705,7 @@
     <t>Bảng số liệu kết quả tài chính (NIKE, Inc.)</t>
   </si>
   <si>
-    <t>Đơn vị triệu USD, trừ khi ghi khác. Số âm để trong ngoặc đơn. Số NIKE công bố có số trang 10-K ở dòng nhỏ ngay dưới (bấm vào số trang để mở báo cáo trên SEC). Số in nghiêng là số nhóm tự tính.</t>
+    <t>Đơn vị triệu USD, trừ khi ghi khác. Số âm để trong ngoặc đơn. Số NIKE công bố có số trang 10‑K ở dòng nhỏ ngay dưới (bấm vào số trang để mở báo cáo trên SEC). Số in nghiêng là số nhóm tự tính.</t>
   </si>
   <si>
     <t>Báo cáo kết quả kinh doanh</t>
@@ -1747,7 +1747,7 @@
     <t>Tăng trưởng doanh thu, theo báo cáo</t>
   </si>
   <si>
-    <t>Tăng trưởng doanh thu, loại trừ tỷ giá (non-GAAP)</t>
+    <t>Tăng trưởng doanh thu, loại trừ tỷ giá (non‑GAAP)</t>
   </si>
   <si>
     <t>Chi phí bán hàng và quản lý / doanh thu</t>
@@ -1762,7 +1762,7 @@
     <t>Biên lợi nhuận sau thuế</t>
   </si>
   <si>
-    <t>EBIT (non-GAAP, định nghĩa của NIKE)</t>
+    <t>EBIT (non‑GAAP, định nghĩa của NIKE)</t>
   </si>
   <si>
     <t>EBIT do NIKE công bố</t>
@@ -1786,40 +1786,40 @@
     <t>ngày</t>
   </si>
   <si>
-    <t>Báo cáo Form 10-K (SEC EDGAR)</t>
-  </si>
-  <si>
-    <t>Form 10-K FY2020, nộp ngày 24/07/2020, số 0000320187-20-000047</t>
-  </si>
-  <si>
-    <t>Form 10-K FY2021, nộp ngày 20/07/2021, số 0000320187-21-000028</t>
-  </si>
-  <si>
-    <t>Form 10-K FY2022, nộp ngày 21/07/2022, số 0000320187-22-000038</t>
-  </si>
-  <si>
-    <t>Form 10-K FY2023, nộp ngày 20/07/2023, số 0000320187-23-000039</t>
-  </si>
-  <si>
-    <t>Form 10-K FY2024, nộp ngày 25/07/2024, số 0000320187-24-000044</t>
-  </si>
-  <si>
-    <t>Form 10-K FY2025, nộp ngày 17/07/2025, số 0000320187-25-000047</t>
-  </si>
-  <si>
-    <t>Form 10-K FY2026, nộp ngày 15/07/2026, số 0000320187-26-000088</t>
+    <t>Báo cáo Form 10‑K (SEC EDGAR)</t>
+  </si>
+  <si>
+    <t>Form 10‑K FY2020, nộp ngày 24/07/2020, số 0000320187-20-000047</t>
+  </si>
+  <si>
+    <t>Form 10‑K FY2021, nộp ngày 20/07/2021, số 0000320187-21-000028</t>
+  </si>
+  <si>
+    <t>Form 10‑K FY2022, nộp ngày 21/07/2022, số 0000320187-22-000038</t>
+  </si>
+  <si>
+    <t>Form 10‑K FY2023, nộp ngày 20/07/2023, số 0000320187-23-000039</t>
+  </si>
+  <si>
+    <t>Form 10‑K FY2024, nộp ngày 25/07/2024, số 0000320187-24-000044</t>
+  </si>
+  <si>
+    <t>Form 10‑K FY2025, nộp ngày 17/07/2025, số 0000320187-25-000047</t>
+  </si>
+  <si>
+    <t>Form 10‑K FY2026, nộp ngày 15/07/2026, số 0000320187-26-000088</t>
   </si>
   <si>
     <t>Phương pháp</t>
   </si>
   <si>
-    <t>–  Số liệu của mỗi năm tài chính được lấy từ báo cáo 10-K của chính năm đó. Khi tính tăng trưởng, số năm trước được lấy ở cột so sánh trong cùng báo cáo, giống cách NIKE tự tính.</t>
-  </si>
-  <si>
-    <t>–  Các số trên báo cáo tài chính được lấy từ dữ liệu XBRL đi kèm mỗi báo cáo 10-K, sau đó đối chiếu với dữ liệu XBRL do SEC công bố và với các bảng trong phần MD&amp;A.</t>
-  </si>
-  <si>
-    <t>–  Các chỉ tiêu chỉ có trong phần MD&amp;A (tăng trưởng loại trừ tỷ giá, doanh số Digital) không có dữ liệu XBRL để đối chiếu, nên được đọc lại thêm một lần ngay trên trang 10-K. Ảnh chụp từng chỗ có ở trang “Đối chiếu 35 số” trên dashboard web.</t>
+    <t>–  Số liệu của mỗi năm tài chính được lấy từ báo cáo 10‑K của chính năm đó. Mỗi báo cáo đều in kèm số của năm trước để so sánh, và tăng trưởng được tính với chính số năm trước này, giống cách NIKE tự tính. Ví dụ: tăng trưởng doanh thu FY2026 tính với doanh thu FY2025 in trong 10‑K FY2026.</t>
+  </si>
+  <si>
+    <t>–  Các số trên báo cáo tài chính được lấy từ dữ liệu XBRL đi kèm mỗi báo cáo 10‑K, sau đó đối chiếu với dữ liệu XBRL do SEC công bố và với các bảng trong phần MD&amp;A.</t>
+  </si>
+  <si>
+    <t>–  Các chỉ tiêu chỉ có trong phần MD&amp;A (tăng trưởng loại trừ tỷ giá, doanh số Digital) không có dữ liệu XBRL để đối chiếu, nên được đọc lại thêm một lần ngay trên trang 10‑K. Ảnh chụp từng chỗ có ở trang “Đối chiếu 35 số” trên dashboard web.</t>
   </si>
   <si>
     <t>–  Các chỉ số do nhóm tự tính dùng đúng công thức ở sheet 04 của bộ dữ liệu Excel. Mỗi lần cập nhật đều kiểm tra lại các phép cộng trừ, chẳng hạn doanh thu trừ giá vốn phải bằng lợi nhuận gộp.</t>
@@ -1846,7 +1846,7 @@
     <t>Bộ dữ liệu Excel (đầy đủ nguồn từng số)</t>
   </si>
   <si>
-    <t>Đối chiếu 35 số trên trang 10-K (ảnh chụp)</t>
+    <t>Đối chiếu 35 số trên trang 10‑K (ảnh chụp)</t>
   </si>
 </sst>
 </file>
@@ -2406,7 +2406,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-F4B5-421A-997A-836B45E9A47C}"/>
+              <c16:uniqueId val="{00000000-2F29-4644-BDFB-BFA650D0E49D}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2526,7 +2526,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-F4B5-421A-997A-836B45E9A47C}"/>
+              <c16:uniqueId val="{00000001-2F29-4644-BDFB-BFA650D0E49D}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2606,7 +2606,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-F4B5-421A-997A-836B45E9A47C}"/>
+              <c16:uniqueId val="{00000002-2F29-4644-BDFB-BFA650D0E49D}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2902,7 +2902,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-684C-447F-AA2D-C23FB3A8C617}"/>
+              <c16:uniqueId val="{00000000-F38A-42F4-8391-D214E227B717}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3166,7 +3166,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-0838-4C6A-8F63-22020B8CD90C}"/>
+              <c16:uniqueId val="{00000000-5BA5-41E9-97DA-6B9A2C406AF8}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3283,7 +3283,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-0838-4C6A-8F63-22020B8CD90C}"/>
+              <c16:uniqueId val="{00000001-5BA5-41E9-97DA-6B9A2C406AF8}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3526,7 +3526,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-EBA7-4880-9044-1C80B83B1A2B}"/>
+              <c16:uniqueId val="{00000000-4BA7-45AB-9AFA-8C33142F1F52}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3606,7 +3606,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-EBA7-4880-9044-1C80B83B1A2B}"/>
+              <c16:uniqueId val="{00000001-4BA7-45AB-9AFA-8C33142F1F52}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3885,7 +3885,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-F417-4F26-A605-000884B78667}"/>
+              <c16:uniqueId val="{00000000-42C3-4D56-95D6-9A3A79660AB8}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3965,7 +3965,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-F417-4F26-A605-000884B78667}"/>
+              <c16:uniqueId val="{00000001-42C3-4D56-95D6-9A3A79660AB8}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4246,7 +4246,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-BEBA-43D1-A3F5-4CD015266C1C}"/>
+              <c16:uniqueId val="{00000000-77F8-4228-9FD8-1F59D809978E}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4520,7 +4520,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-D4EC-4C5E-B7BC-951AD9C5D377}"/>
+              <c16:uniqueId val="{00000000-C6B0-450E-8955-B0E484C8105B}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4749,7 +4749,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-0B06-4BD7-B808-7446FB41F79A}"/>
+              <c16:uniqueId val="{00000000-CB1D-4F8D-AFC9-722570DD9FE3}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4831,7 +4831,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-0B06-4BD7-B808-7446FB41F79A}"/>
+              <c16:uniqueId val="{00000001-CB1D-4F8D-AFC9-722570DD9FE3}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4965,7 +4965,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-0B06-4BD7-B808-7446FB41F79A}"/>
+              <c16:uniqueId val="{00000002-CB1D-4F8D-AFC9-722570DD9FE3}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -5263,7 +5263,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-2235-45FF-898C-5A0FF4324209}"/>
+              <c16:uniqueId val="{00000000-4475-421A-BF38-359726BE54BE}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -5525,7 +5525,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-ABB1-4BDC-8308-E446A604ACBE}"/>
+              <c16:uniqueId val="{00000000-453E-4183-BBFC-68E8854B08C4}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -5818,7 +5818,7 @@
             <xdr:cNvPr id="6" name="sl_tblNam1">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E4D652F0-2B89-4882-22A6-07FF7C6CFCD0}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{898BE571-BB1F-F0F8-4A04-B04E93B7F12F}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -5896,7 +5896,7 @@
             <xdr:cNvPr id="7" name="sl_tblCoSo1">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3046B924-557A-C8DD-B57C-D05EC064C562}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{802F3EF7-80B9-907B-050E-E6B67DB25ECF}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -6195,7 +6195,7 @@
             <xdr:cNvPr id="8" name="sl_tblNam2">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5F74DE0C-BF96-D71B-1C77-5D1CB31AFB1B}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4E424159-FBDB-164A-3F21-3EEE58CDE710}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -6257,7 +6257,7 @@
 </file>
 
 <file path=xl/slicerCaches/slicerCache1.xml><?xml version="1.0" encoding="utf-8"?>
-<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_Năm_tài_chính" xr10:uid="{9FCC4910-C2E4-4797-9A4D-FAE540B2F395}" sourceName="Năm tài chính">
+<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_Năm_tài_chính" xr10:uid="{03BD7112-6FEF-4760-BFB6-51635299B39F}" sourceName="Năm tài chính">
   <extLst>
     <x:ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{2F2917AC-EB37-4324-AD4E-5DD8C200BD13}">
       <x15:tableSlicerCache tableId="1" column="1"/>
@@ -6267,7 +6267,7 @@
 </file>
 
 <file path=xl/slicerCaches/slicerCache2.xml><?xml version="1.0" encoding="utf-8"?>
-<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_Cơ_sở_tính_tăng_trưởng" xr10:uid="{801E203E-EBBE-48C2-8934-94D04E7BFD79}" sourceName="Cơ sở tính tăng trưởng">
+<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_Cơ_sở_tính_tăng_trưởng" xr10:uid="{8D8757FE-B314-4FDA-8A78-70A4D721316F}" sourceName="Cơ sở tính tăng trưởng">
   <extLst>
     <x:ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{2F2917AC-EB37-4324-AD4E-5DD8C200BD13}">
       <x15:tableSlicerCache tableId="2" column="1" sortOrder="descending"/>
@@ -6278,14 +6278,14 @@
 
 <file path=xl/slicers/slicer1.xml><?xml version="1.0" encoding="utf-8"?>
 <slicers xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10">
-  <slicer name="sl_tblNam1" xr10:uid="{4BE8442A-538E-4739-87F0-504999243F58}" cache="Slicer_Năm_tài_chính" caption="Năm tài chính" columnCount="7" rowHeight="220133"/>
-  <slicer name="sl_tblCoSo1" xr10:uid="{B8682230-0F0F-4EE5-BDAA-2321871BD854}" cache="Slicer_Cơ_sở_tính_tăng_trưởng" caption="Cơ sở tính tăng trưởng" columnCount="2" rowHeight="220133"/>
+  <slicer name="sl_tblNam1" xr10:uid="{924E9E88-95C2-4E86-9D57-3B737C02EB15}" cache="Slicer_Năm_tài_chính" caption="Năm tài chính" columnCount="7" rowHeight="220133"/>
+  <slicer name="sl_tblCoSo1" xr10:uid="{898B0C09-4C02-4883-A3F4-B5F567473F7E}" cache="Slicer_Cơ_sở_tính_tăng_trưởng" caption="Cơ sở tính tăng trưởng" columnCount="2" rowHeight="220133"/>
 </slicers>
 </file>
 
 <file path=xl/slicers/slicer2.xml><?xml version="1.0" encoding="utf-8"?>
 <slicers xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10">
-  <slicer name="sl_tblNam2" xr10:uid="{89E8F336-86D3-4511-9EE7-96D8152F0705}" cache="Slicer_Năm_tài_chính" caption="Năm tài chính" columnCount="7" rowHeight="220133"/>
+  <slicer name="sl_tblNam2" xr10:uid="{D1B16228-0E63-4D6A-96A2-10A253B1725B}" cache="Slicer_Năm_tài_chính" caption="Năm tài chính" columnCount="7" rowHeight="220133"/>
 </slicers>
 </file>
 
@@ -6744,7 +6744,7 @@
       <c r="G13" s="33"/>
       <c r="I13" s="35" t="str">
         <f>'Dữ liệu biểu đồ'!$C$27</f>
-        <v>Tỷ trọng NIKE Direct trong doanh thu NIKE Brand là 34,8% ở FY2020 và 39,2% ở FY2026, cao nhất 43,7% (FY2023). Doanh thu NIKE Direct đi từ 12,4 đến 17,7 tỷ USD, còn bán buôn từ 23,2 đến 27,5 tỷ USD.</v>
+        <v>Tỷ trọng NIKE Direct trong doanh thu NIKE Brand là 34,8% ở FY2020 và 39,2% ở FY2026, cao nhất 43,7% (FY2023). Doanh thu NIKE Direct đi từ 12,4 đến 17,7 tỷ USD, còn bán buôn từ 23,2 đến 27,5 tỷ USD.</v>
       </c>
       <c r="J13" s="35"/>
       <c r="K13" s="35"/>
@@ -6838,8 +6838,8 @@
     </row>
     <row r="38" spans="2:13" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B38" s="38" t="str">
-        <f>"Nguồn: thuyết minh “Revenues” trong Form 10-K (bảng phân tách doanh thu, cột Total NIKE Brand). Tỷ trọng do nhóm tự tính."&amp;'Dữ liệu biểu đồ'!$C$31</f>
-        <v>Nguồn: thuyết minh “Revenues” trong Form 10-K (bảng phân tách doanh thu, cột Total NIKE Brand). Tỷ trọng do nhóm tự tính. Báo cáo: 10-K FY2020–FY2026 (danh sách ở sheet “Nguồn và phương pháp”).</v>
+        <f>"Nguồn: thuyết minh “Revenues” trong Form 10‑K (bảng phân tách doanh thu, cột Total NIKE Brand). Tỷ trọng do nhóm tự tính."&amp;'Dữ liệu biểu đồ'!$C$31</f>
+        <v>Nguồn: thuyết minh “Revenues” trong Form 10‑K (bảng phân tách doanh thu, cột Total NIKE Brand). Tỷ trọng do nhóm tự tính. Báo cáo: 10‑K FY2020–FY2026 (danh sách ở sheet “Nguồn và phương pháp”).</v>
       </c>
       <c r="C38" s="38"/>
       <c r="D38" s="38"/>
@@ -6882,7 +6882,7 @@
       <c r="G41" s="37"/>
       <c r="H41" s="37" t="str">
         <f>'Dữ liệu biểu đồ'!$C$29</f>
-        <v>Thay đổi so với năm trước (%), theo báo cáo, phạm vi NIKE Brand. Nhóm tự tính từ 10-K.</v>
+        <v>Thay đổi so với năm trước (%), theo báo cáo, phạm vi NIKE Brand. Nhóm tự tính từ 10‑K.</v>
       </c>
       <c r="I41" s="37"/>
       <c r="J41" s="37"/>
@@ -6895,8 +6895,8 @@
     <row r="44" spans="2:13" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="59" spans="2:13" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B59" s="38" t="str">
-        <f>"Nguồn: thuyết minh “Revenues” trong Form 10-K."&amp;'Dữ liệu biểu đồ'!$C$31</f>
-        <v>Nguồn: thuyết minh “Revenues” trong Form 10-K. Báo cáo: 10-K FY2020–FY2026 (danh sách ở sheet “Nguồn và phương pháp”).</v>
+        <f>"Nguồn: thuyết minh “Revenues” trong Form 10‑K."&amp;'Dữ liệu biểu đồ'!$C$31</f>
+        <v>Nguồn: thuyết minh “Revenues” trong Form 10‑K. Báo cáo: 10‑K FY2020–FY2026 (danh sách ở sheet “Nguồn và phương pháp”).</v>
       </c>
       <c r="C59" s="38"/>
       <c r="D59" s="38"/>
@@ -6905,7 +6905,7 @@
       <c r="G59" s="38"/>
       <c r="H59" s="38" t="str">
         <f>'Dữ liệu biểu đồ'!$C$30&amp;'Dữ liệu biểu đồ'!$C$31</f>
-        <v>Nguồn: thuyết minh “Revenues” trong Form 10-K. Tăng trưởng tính từ số năm nay và số năm trước trong cùng 10-K. Báo cáo: 10-K FY2020–FY2026 (danh sách ở sheet “Nguồn và phương pháp”).</v>
+        <v>Nguồn: thuyết minh “Revenues” trong Form 10‑K. Tăng trưởng tính từ số năm nay và số năm trước trong cùng 10‑K. Báo cáo: 10‑K FY2020–FY2026 (danh sách ở sheet “Nguồn và phương pháp”).</v>
       </c>
       <c r="I59" s="38"/>
       <c r="J59" s="38"/>
@@ -7070,7 +7070,7 @@
     <row r="78" spans="2:13" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B78" s="38" t="str">
         <f>"Nguồn: MD&amp;A (Item 7), đoạn nói về NIKE Direct. Số NIKE Direct lấy từ thuyết minh “Revenues”."&amp;'Dữ liệu biểu đồ'!$C$31</f>
-        <v>Nguồn: MD&amp;A (Item 7), đoạn nói về NIKE Direct. Số NIKE Direct lấy từ thuyết minh “Revenues”. Báo cáo: 10-K FY2020–FY2026 (danh sách ở sheet “Nguồn và phương pháp”).</v>
+        <v>Nguồn: MD&amp;A (Item 7), đoạn nói về NIKE Direct. Số NIKE Direct lấy từ thuyết minh “Revenues”. Báo cáo: 10‑K FY2020–FY2026 (danh sách ở sheet “Nguồn và phương pháp”).</v>
       </c>
       <c r="C78" s="38"/>
       <c r="D78" s="38"/>
@@ -8242,7 +8242,7 @@
       <c r="G13" s="33"/>
       <c r="I13" s="35" t="str">
         <f>'Dữ liệu biểu đồ'!$C$28</f>
-        <v>Doanh thu NIKE, Inc. đi từ 37,4 (FY2020) đến 46,4 tỷ USD (FY2026). Biên lợi nhuận gộp là 43,4% (FY2020) và 42,9% (FY2026), còn biên EBIT (non-GAAP) là 8,0% (FY2020) và 8,3% (FY2026), cao nhất 15,5% (FY2021). Hàng tồn kho cuối kỳ đi từ 7,4 đến 7,5 tỷ USD.</v>
+        <v>Doanh thu NIKE, Inc. đi từ 37,4 (FY2020) đến 46,4 tỷ USD (FY2026). Biên lợi nhuận gộp là 43,4% (FY2020) và 42,9% (FY2026), còn biên EBIT (non‑GAAP) là 8,0% (FY2020) và 8,3% (FY2026), cao nhất 15,5% (FY2021). Hàng tồn kho cuối kỳ đi từ 7,4 đến 7,5 tỷ USD.</v>
       </c>
       <c r="J13" s="35"/>
       <c r="K13" s="35"/>
@@ -8345,21 +8345,21 @@
     <row r="34" spans="2:13" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B34" s="38" t="str">
         <f>"Nguồn: Consolidated Statements of Income."&amp;'Dữ liệu biểu đồ'!$C$31</f>
-        <v>Nguồn: Consolidated Statements of Income. Báo cáo: 10-K FY2020–FY2026 (danh sách ở sheet “Nguồn và phương pháp”).</v>
+        <v>Nguồn: Consolidated Statements of Income. Báo cáo: 10‑K FY2020–FY2026 (danh sách ở sheet “Nguồn và phương pháp”).</v>
       </c>
       <c r="C34" s="38"/>
       <c r="D34" s="38"/>
       <c r="E34" s="38"/>
       <c r="F34" s="38" t="str">
         <f>"Nguồn: Consolidated Statements of Income. Biên lợi nhuận gộp do nhóm tự tính."&amp;'Dữ liệu biểu đồ'!$C$31</f>
-        <v>Nguồn: Consolidated Statements of Income. Biên lợi nhuận gộp do nhóm tự tính. Báo cáo: 10-K FY2020–FY2026 (danh sách ở sheet “Nguồn và phương pháp”).</v>
+        <v>Nguồn: Consolidated Statements of Income. Biên lợi nhuận gộp do nhóm tự tính. Báo cáo: 10‑K FY2020–FY2026 (danh sách ở sheet “Nguồn và phương pháp”).</v>
       </c>
       <c r="G34" s="38"/>
       <c r="H34" s="38"/>
       <c r="I34" s="38"/>
       <c r="J34" s="38" t="str">
         <f>"Nguồn: Consolidated Statements of Income. Tỷ lệ do nhóm tự tính. Nhãn trên cột là tổng SG&amp;A / doanh thu."&amp;'Dữ liệu biểu đồ'!$C$31</f>
-        <v>Nguồn: Consolidated Statements of Income. Tỷ lệ do nhóm tự tính. Nhãn trên cột là tổng SG&amp;A / doanh thu. Báo cáo: 10-K FY2020–FY2026 (danh sách ở sheet “Nguồn và phương pháp”).</v>
+        <v>Nguồn: Consolidated Statements of Income. Tỷ lệ do nhóm tự tính. Nhãn trên cột là tổng SG&amp;A / doanh thu. Báo cáo: 10‑K FY2020–FY2026 (danh sách ở sheet “Nguồn và phương pháp”).</v>
       </c>
       <c r="K34" s="38"/>
       <c r="L34" s="38"/>
@@ -8408,21 +8408,21 @@
     <row r="51" spans="2:13" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="38" t="str">
         <f>"Nguồn: bảng EBIT trong MD&amp;A (Item 7) và Consolidated Statements of Income. Biên EBIT do nhóm tự tính."&amp;'Dữ liệu biểu đồ'!$C$31</f>
-        <v>Nguồn: bảng EBIT trong MD&amp;A (Item 7) và Consolidated Statements of Income. Biên EBIT do nhóm tự tính. Báo cáo: 10-K FY2020–FY2026 (danh sách ở sheet “Nguồn và phương pháp”).</v>
+        <v>Nguồn: bảng EBIT trong MD&amp;A (Item 7) và Consolidated Statements of Income. Biên EBIT do nhóm tự tính. Báo cáo: 10‑K FY2020–FY2026 (danh sách ở sheet “Nguồn và phương pháp”).</v>
       </c>
       <c r="C51" s="38"/>
       <c r="D51" s="38"/>
       <c r="E51" s="38"/>
       <c r="F51" s="38" t="str">
         <f>"Nguồn: Consolidated Balance Sheets."&amp;'Dữ liệu biểu đồ'!$C$31</f>
-        <v>Nguồn: Consolidated Balance Sheets. Báo cáo: 10-K FY2020–FY2026 (danh sách ở sheet “Nguồn và phương pháp”).</v>
+        <v>Nguồn: Consolidated Balance Sheets. Báo cáo: 10‑K FY2020–FY2026 (danh sách ở sheet “Nguồn và phương pháp”).</v>
       </c>
       <c r="G51" s="38"/>
       <c r="H51" s="38"/>
       <c r="I51" s="38"/>
       <c r="J51" s="38" t="str">
         <f>"Nguồn: Consolidated Balance Sheets và Statements of Income. Chỉ số do nhóm tự tính."&amp;'Dữ liệu biểu đồ'!$C$31</f>
-        <v>Nguồn: Consolidated Balance Sheets và Statements of Income. Chỉ số do nhóm tự tính. Báo cáo: 10-K FY2020–FY2026 (danh sách ở sheet “Nguồn và phương pháp”).</v>
+        <v>Nguồn: Consolidated Balance Sheets và Statements of Income. Chỉ số do nhóm tự tính. Báo cáo: 10‑K FY2020–FY2026 (danh sách ở sheet “Nguồn và phương pháp”).</v>
       </c>
       <c r="K51" s="38"/>
       <c r="L51" s="38"/>
@@ -10196,7 +10196,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="5" spans="2:4" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:4" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="21" t="s">
         <v>528</v>
       </c>
@@ -11155,8 +11155,8 @@
         <v>103</v>
       </c>
       <c r="C27" t="str">
-        <f>IF($C$21=$C$22,"Trong FY"&amp;$C$21&amp;", NIKE Direct chiếm "&amp;INDEX($W$5:$W$11,$C$21-2019)&amp;" doanh thu NIKE Brand ("&amp;INDEX($Y$5:$Y$11,$C$21-2019)&amp;" tỷ USD), còn bán buôn chiếm "&amp;INDEX($X$5:$X$11,$C$21-2019)&amp;" ("&amp;INDEX($Z$5:$Z$11,$C$21-2019)&amp;" tỷ USD).","Tỷ trọng NIKE Direct trong doanh thu NIKE Brand là "&amp;INDEX($W$5:$W$11,$C$21-2019)&amp;" ở FY"&amp;$C$21&amp;" và "&amp;INDEX($W$5:$W$11,$C$22-2019)&amp;" ở FY"&amp;$C$22&amp;IF(AND($C$24&lt;&gt;$C$21,$C$24&lt;&gt;$C$22),", cao nhất "&amp;INDEX($W$5:$W$11,$C$24-2019)&amp;" (FY"&amp;$C$24&amp;")","")&amp;IF(AND($C$25&lt;&gt;$C$21,$C$25&lt;&gt;$C$22),IF(AND($C$24&lt;&gt;$C$21,$C$24&lt;&gt;$C$22)," và thấp nhất ",", thấp nhất ")&amp;INDEX($W$5:$W$11,$C$25-2019)&amp;" (FY"&amp;$C$25&amp;")","")&amp;". Doanh thu NIKE Direct đi từ "&amp;INDEX($Y$5:$Y$11,$C$21-2019)&amp;" đến "&amp;INDEX($Y$5:$Y$11,$C$22-2019)&amp;" tỷ USD, còn bán buôn từ "&amp;INDEX($Z$5:$Z$11,$C$21-2019)&amp;" đến "&amp;INDEX($Z$5:$Z$11,$C$22-2019)&amp;" tỷ USD.")</f>
-        <v>Tỷ trọng NIKE Direct trong doanh thu NIKE Brand là 34,8% ở FY2020 và 39,2% ở FY2026, cao nhất 43,7% (FY2023). Doanh thu NIKE Direct đi từ 12,4 đến 17,7 tỷ USD, còn bán buôn từ 23,2 đến 27,5 tỷ USD.</v>
+        <f>IF($C$21=$C$22,"Trong FY"&amp;$C$21&amp;", NIKE Direct chiếm "&amp;INDEX($W$5:$W$11,$C$21-2019)&amp;" doanh thu NIKE Brand ("&amp;INDEX($Y$5:$Y$11,$C$21-2019)&amp;" tỷ USD), còn bán buôn chiếm "&amp;INDEX($X$5:$X$11,$C$21-2019)&amp;" ("&amp;INDEX($Z$5:$Z$11,$C$21-2019)&amp;" tỷ USD).","Tỷ trọng NIKE Direct trong doanh thu NIKE Brand là "&amp;INDEX($W$5:$W$11,$C$21-2019)&amp;" ở FY"&amp;$C$21&amp;" và "&amp;INDEX($W$5:$W$11,$C$22-2019)&amp;" ở FY"&amp;$C$22&amp;IF(AND($C$24&lt;&gt;$C$21,$C$24&lt;&gt;$C$22),", cao nhất "&amp;INDEX($W$5:$W$11,$C$24-2019)&amp;" (FY"&amp;$C$24&amp;")","")&amp;IF(AND($C$25&lt;&gt;$C$21,$C$25&lt;&gt;$C$22),IF(AND($C$24&lt;&gt;$C$21,$C$24&lt;&gt;$C$22)," và thấp nhất ",", thấp nhất ")&amp;INDEX($W$5:$W$11,$C$25-2019)&amp;" (FY"&amp;$C$25&amp;")","")&amp;". Doanh thu NIKE Direct đi từ "&amp;INDEX($Y$5:$Y$11,$C$21-2019)&amp;" đến "&amp;INDEX($Y$5:$Y$11,$C$22-2019)&amp;" tỷ USD, còn bán buôn từ "&amp;INDEX($Z$5:$Z$11,$C$21-2019)&amp;" đến "&amp;INDEX($Z$5:$Z$11,$C$22-2019)&amp;" tỷ USD.")</f>
+        <v>Tỷ trọng NIKE Direct trong doanh thu NIKE Brand là 34,8% ở FY2020 và 39,2% ở FY2026, cao nhất 43,7% (FY2023). Doanh thu NIKE Direct đi từ 12,4 đến 17,7 tỷ USD, còn bán buôn từ 23,2 đến 27,5 tỷ USD.</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
@@ -11164,8 +11164,8 @@
         <v>104</v>
       </c>
       <c r="C28" t="str">
-        <f>IF($C$21=$C$22,"Trong FY"&amp;$C$21&amp;", doanh thu NIKE, Inc. là "&amp;INDEX($AA$5:$AA$11,$C$21-2019)&amp;" tỷ USD, biên lợi nhuận gộp "&amp;INDEX($AB$5:$AB$11,$C$21-2019)&amp;", biên EBIT (non-GAAP) "&amp;INDEX($AC$5:$AC$11,$C$21-2019)&amp;", hàng tồn kho cuối kỳ "&amp;INDEX($AD$5:$AD$11,$C$21-2019)&amp;" tỷ USD.","Doanh thu NIKE, Inc. đi từ "&amp;INDEX($AA$5:$AA$11,$C$21-2019)&amp;" (FY"&amp;$C$21&amp;") đến "&amp;INDEX($AA$5:$AA$11,$C$22-2019)&amp;" tỷ USD (FY"&amp;$C$22&amp;"). Biên lợi nhuận gộp là "&amp;INDEX($AB$5:$AB$11,$C$21-2019)&amp;" (FY"&amp;$C$21&amp;") và "&amp;INDEX($AB$5:$AB$11,$C$22-2019)&amp;" (FY"&amp;$C$22&amp;"), còn biên EBIT (non-GAAP) là "&amp;INDEX($AC$5:$AC$11,$C$21-2019)&amp;" (FY"&amp;$C$21&amp;") và "&amp;INDEX($AC$5:$AC$11,$C$22-2019)&amp;" (FY"&amp;$C$22&amp;")"&amp;IF(AND($C$26&lt;&gt;$C$21,$C$26&lt;&gt;$C$22),", cao nhất "&amp;INDEX($AC$5:$AC$11,$C$26-2019)&amp;" (FY"&amp;$C$26&amp;")","")&amp;". Hàng tồn kho cuối kỳ đi từ "&amp;INDEX($AD$5:$AD$11,$C$21-2019)&amp;" đến "&amp;INDEX($AD$5:$AD$11,$C$22-2019)&amp;" tỷ USD.")</f>
-        <v>Doanh thu NIKE, Inc. đi từ 37,4 (FY2020) đến 46,4 tỷ USD (FY2026). Biên lợi nhuận gộp là 43,4% (FY2020) và 42,9% (FY2026), còn biên EBIT (non-GAAP) là 8,0% (FY2020) và 8,3% (FY2026), cao nhất 15,5% (FY2021). Hàng tồn kho cuối kỳ đi từ 7,4 đến 7,5 tỷ USD.</v>
+        <f>IF($C$21=$C$22,"Trong FY"&amp;$C$21&amp;", doanh thu NIKE, Inc. là "&amp;INDEX($AA$5:$AA$11,$C$21-2019)&amp;" tỷ USD, biên lợi nhuận gộp "&amp;INDEX($AB$5:$AB$11,$C$21-2019)&amp;", biên EBIT (non‑GAAP) "&amp;INDEX($AC$5:$AC$11,$C$21-2019)&amp;", hàng tồn kho cuối kỳ "&amp;INDEX($AD$5:$AD$11,$C$21-2019)&amp;" tỷ USD.","Doanh thu NIKE, Inc. đi từ "&amp;INDEX($AA$5:$AA$11,$C$21-2019)&amp;" (FY"&amp;$C$21&amp;") đến "&amp;INDEX($AA$5:$AA$11,$C$22-2019)&amp;" tỷ USD (FY"&amp;$C$22&amp;"). Biên lợi nhuận gộp là "&amp;INDEX($AB$5:$AB$11,$C$21-2019)&amp;" (FY"&amp;$C$21&amp;") và "&amp;INDEX($AB$5:$AB$11,$C$22-2019)&amp;" (FY"&amp;$C$22&amp;"), còn biên EBIT (non‑GAAP) là "&amp;INDEX($AC$5:$AC$11,$C$21-2019)&amp;" (FY"&amp;$C$21&amp;") và "&amp;INDEX($AC$5:$AC$11,$C$22-2019)&amp;" (FY"&amp;$C$22&amp;")"&amp;IF(AND($C$26&lt;&gt;$C$21,$C$26&lt;&gt;$C$22),", cao nhất "&amp;INDEX($AC$5:$AC$11,$C$26-2019)&amp;" (FY"&amp;$C$26&amp;")","")&amp;". Hàng tồn kho cuối kỳ đi từ "&amp;INDEX($AD$5:$AD$11,$C$21-2019)&amp;" đến "&amp;INDEX($AD$5:$AD$11,$C$22-2019)&amp;" tỷ USD.")</f>
+        <v>Doanh thu NIKE, Inc. đi từ 37,4 (FY2020) đến 46,4 tỷ USD (FY2026). Biên lợi nhuận gộp là 43,4% (FY2020) và 42,9% (FY2026), còn biên EBIT (non‑GAAP) là 8,0% (FY2020) và 8,3% (FY2026), cao nhất 15,5% (FY2021). Hàng tồn kho cuối kỳ đi từ 7,4 đến 7,5 tỷ USD.</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
@@ -11173,8 +11173,8 @@
         <v>105</v>
       </c>
       <c r="C29" t="str">
-        <f>IF('Dữ liệu biểu đồ'!$C$20="cn","Thay đổi so với năm trước (%), loại trừ tỷ giá, phạm vi NIKE Brand. Số do NIKE công bố (non-GAAP).","Thay đổi so với năm trước (%), theo báo cáo, phạm vi NIKE Brand. Nhóm tự tính từ 10-K.")</f>
-        <v>Thay đổi so với năm trước (%), theo báo cáo, phạm vi NIKE Brand. Nhóm tự tính từ 10-K.</v>
+        <f>IF('Dữ liệu biểu đồ'!$C$20="cn","Thay đổi so với năm trước (%), loại trừ tỷ giá, phạm vi NIKE Brand. Số do NIKE công bố (non‑GAAP).","Thay đổi so với năm trước (%), theo báo cáo, phạm vi NIKE Brand. Nhóm tự tính từ 10‑K.")</f>
+        <v>Thay đổi so với năm trước (%), theo báo cáo, phạm vi NIKE Brand. Nhóm tự tính từ 10‑K.</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
@@ -11182,8 +11182,8 @@
         <v>106</v>
       </c>
       <c r="C30" t="str">
-        <f>IF('Dữ liệu biểu đồ'!$C$20="cn","Nguồn: bảng doanh thu trong MD&amp;A (Item 7), cột “% change excluding currency changes”. NIKE làm tròn đến số nguyên.","Nguồn: thuyết minh “Revenues” trong Form 10-K. Tăng trưởng tính từ số năm nay và số năm trước trong cùng 10-K.")</f>
-        <v>Nguồn: thuyết minh “Revenues” trong Form 10-K. Tăng trưởng tính từ số năm nay và số năm trước trong cùng 10-K.</v>
+        <f>IF('Dữ liệu biểu đồ'!$C$20="cn","Nguồn: bảng doanh thu trong MD&amp;A (Item 7), cột “% change excluding currency changes”. NIKE làm tròn đến số nguyên.","Nguồn: thuyết minh “Revenues” trong Form 10‑K. Tăng trưởng tính từ số năm nay và số năm trước trong cùng 10‑K.")</f>
+        <v>Nguồn: thuyết minh “Revenues” trong Form 10‑K. Tăng trưởng tính từ số năm nay và số năm trước trong cùng 10‑K.</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
@@ -11191,8 +11191,8 @@
         <v>107</v>
       </c>
       <c r="C31" t="str">
-        <f>" Báo cáo: 10-K FY"&amp;'Dữ liệu biểu đồ'!$C$21&amp;IF('Dữ liệu biểu đồ'!$C$21='Dữ liệu biểu đồ'!$C$22,"","–FY"&amp;'Dữ liệu biểu đồ'!$C$22)&amp;" (danh sách ở sheet “Nguồn và phương pháp”)."</f>
-        <v xml:space="preserve"> Báo cáo: 10-K FY2020–FY2026 (danh sách ở sheet “Nguồn và phương pháp”).</v>
+        <f>" Báo cáo: 10‑K FY"&amp;'Dữ liệu biểu đồ'!$C$21&amp;IF('Dữ liệu biểu đồ'!$C$21='Dữ liệu biểu đồ'!$C$22,"","–FY"&amp;'Dữ liệu biểu đồ'!$C$22)&amp;" (danh sách ở sheet “Nguồn và phương pháp”)."</f>
+        <v xml:space="preserve"> Báo cáo: 10‑K FY2020–FY2026 (danh sách ở sheet “Nguồn và phương pháp”).</v>
       </c>
     </row>
     <row r="45" spans="1:16" ht="13" x14ac:dyDescent="0.25">
